--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.08571428571428572</v>
+        <v>0.1</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.09154929577464789</v>
+        <v>0.1126760563380282</v>
       </c>
       <c r="D2">
-        <v>0.9148936170212766</v>
+        <v>0.9</v>
       </c>
       <c r="E2">
         <v>140</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
